--- a/associations_973_guyane.xlsx
+++ b/associations_973_guyane.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Associations 973" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Communes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="À vérifier" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Communes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Associations 973'!$A$1:$G$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Associations 973'!$A$1:$G$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -482,32 +483,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amicale Bouliste de Macouria</t>
+          <t>ASA Club 973 (Grand Prix Rallye Somasco)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jean.maledon@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0694 42 72 34</t>
-        </is>
-      </c>
+          <t>asaclub973@orange.fr</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/amicale-bouliste-de-macouria/</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/RDV-AVRIL-2024-.pdf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,32 +516,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amicale shotokan de Macouria</t>
+          <t>Cryo Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>armand.prudent@wanadoo.fr</t>
+          <t>cryoteam.kourou@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0694 44 19 88</t>
+          <t>0694 24 49 99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/amicale-shotokan-de-macouria/</t>
+          <t>https://www.ville-kourou.fr/le-cross-des-wayam-revient-pour-une-2eme-edition-a-kourou/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -556,32 +553,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ara de Macouria</t>
+          <t>Toucan Athletic Club de Kourou (TAC)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ara.de.macouria@wanadoo.fr</t>
+          <t>picmuche@hotmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0694 23 62 10</t>
+          <t>0594 32 02 91 / 0594 32 90 18 / 0694 22 32 45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ara-de-macouria/</t>
+          <t>https://www.ville-kourou.fr/agenda/30eme-marathon-de-lespace/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -593,7 +590,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ass. Culturelle et Sportive de Macouria</t>
+          <t>Amicale Bouliste de Macouria</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,17 +600,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iswear1@hotmail.com</t>
+          <t>jean.maledon@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0694 27 02 42</t>
+          <t>0694 42 72 34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-culturelle-et-sportive-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/amicale-bouliste-de-macouria/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -630,7 +627,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ass. Malaïka</t>
+          <t>Amicale shotokan de Macouria</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -640,17 +637,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>garrouch.sylvain@orange.fr</t>
+          <t>armand.prudent@wanadoo.fr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0694 40 84 32</t>
+          <t>0694 44 19 88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-malaika/</t>
+          <t>https://www.macouria.fr/annuaire/amicale-shotokan-de-macouria/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -667,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ass. Nova Géracao Capoeira</t>
+          <t>Ara de Macouria</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -677,17 +674,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>geracaocapoeira.macouria@gmail.com</t>
+          <t>ara.de.macouria@wanadoo.fr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0694 24 55 51</t>
+          <t>0694 23 62 10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-nova-geracao-capoeira/</t>
+          <t>https://www.macouria.fr/annuaire/ara-de-macouria/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -704,7 +701,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ass.Maliwe</t>
+          <t>Ass. Culturelle et Sportive de Macouria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,17 +711,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maliwesports@gmail.com</t>
+          <t>iswear1@hotmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0694 21 26 42</t>
+          <t>0694 27 02 42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-maliwe/</t>
+          <t>https://www.macouria.fr/annuaire/ass-culturelle-et-sportive-de-macouria/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +738,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ass.Sportive et Culturelle de la Carapa</t>
+          <t>Ass. Malaïka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -751,17 +748,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>asccarapa@outlook.com</t>
+          <t>garrouch.sylvain@orange.fr</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0694 96 36 36</t>
+          <t>0694 40 84 32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-sportive-et-culturelle-de-la-carapa/</t>
+          <t>https://www.macouria.fr/annuaire/ass-malaika/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -778,7 +775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ass.Sportive et Culturelle de soula</t>
+          <t>Ass. Nova Géracao Capoeira</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -788,17 +785,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ascsoula@gmail.com</t>
+          <t>geracaocapoeira.macouria@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0694 24 30 09</t>
+          <t>0694 24 55 51</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-sportive-et-culturelle-de-soula/</t>
+          <t>https://www.macouria.fr/annuaire/ass-nova-geracao-capoeira/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -815,7 +812,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASSOCIATION DE NATATION DE MACOURIA</t>
+          <t>Ass.Maliwe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,17 +822,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>andm97355@gmail.com</t>
+          <t>maliwesports@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06 94 40 94 07</t>
+          <t>0694 21 26 42</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/association-de-natation-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/ass-maliwe/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -852,7 +849,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASSOCIATION SPORTIVE AZUR DE MACOURIA</t>
+          <t>Ass.Sportive et Culturelle de la Carapa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -862,17 +859,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact@asambasket.com</t>
+          <t>asccarapa@outlook.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>06 94 21 36 26</t>
+          <t>0694 96 36 36</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/association-sportive-azur-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/ass-sportive-et-culturelle-de-la-carapa/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -889,7 +886,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Athletisme club de Soula</t>
+          <t>Ass.Sportive et Culturelle de soula</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -899,17 +896,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>huguette.rene@gmail.com</t>
+          <t>ascsoula@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0694 20 38 65 / 0694 09 00 67</t>
+          <t>0694 24 30 09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/athletisme-club-de-soula/</t>
+          <t>https://www.macouria.fr/annuaire/ass-sportive-et-culturelle-de-soula/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -926,7 +923,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boxe ThaÏ de Macouria Matoury (BTMM)</t>
+          <t>ASSOCIATION DE NATATION DE MACOURIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -936,17 +933,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>luc-adele.lambert@wanadoo.fr</t>
+          <t>andm97355@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0694 26 64 90</t>
+          <t>06 94 40 94 07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/boxe-thai-de-macouria-matoury-btmm/</t>
+          <t>https://www.macouria.fr/annuaire/association-de-natation-de-macouria/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -963,7 +960,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Club de tir sportif de Macouria</t>
+          <t>ASSOCIATION SPORTIVE AZUR DE MACOURIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -973,17 +970,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ctsdemacouria@gmail.com</t>
+          <t>contact@asambasket.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0694 26 08 25 / 0594 30 02 67</t>
+          <t>06 94 21 36 26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/club-de-tir-sportif-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/association-sportive-azur-de-macouria/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1000,7 +997,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EQUILIBRE WORKOUT</t>
+          <t>Athletisme club de Soula</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1010,17 +1007,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>judorvf@gmail.com</t>
+          <t>huguette.rene@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06 71 99 62 03</t>
+          <t>0694 20 38 65 / 0694 09 00 67</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/equilibre-workout/</t>
+          <t>https://www.macouria.fr/annuaire/athletisme-club-de-soula/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1037,7 +1034,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Espace Gym 2000</t>
+          <t>Athlétisme club de Soula (organisateur du Cross Roger Canut)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1047,22 +1044,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>espace.gym.2000@orange.fr</t>
+          <t>huguette.rene@orange.fr</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0694 38 29 09</t>
+          <t>0694 20 38 65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/espace-gym-2000/</t>
+          <t>https://www.macouria.fr/agenda/cross-roger-canut-2024-6eme-edition/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1074,7 +1071,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Futsal Club de Soula</t>
+          <t>Boxe ThaÏ de Macouria Matoury (BTMM)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1084,17 +1081,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>futsalclubsoula@gmail.com</t>
+          <t>luc-adele.lambert@wanadoo.fr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0694 44 50 03</t>
+          <t>0694 26 64 90</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/futsal-club-de-soula/</t>
+          <t>https://www.macouria.fr/annuaire/boxe-thai-de-macouria-matoury-btmm/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1111,7 +1108,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Judo Club de Tonate Macouria</t>
+          <t>Club de tir sportif de Macouria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1121,17 +1118,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>frederic.munos@cnes.fr</t>
+          <t>ctsdemacouria@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0694 26 46 35 / 0694 13 68 96</t>
+          <t>0694 26 08 25 / 0594 30 02 67</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/judo-club-de-tonate-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/club-de-tir-sportif-de-macouria/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1148,7 +1145,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karting de Guyane</t>
+          <t>EQUILIBRE WORKOUT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1158,17 +1155,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>m.girard@hotmail.fr</t>
+          <t>judorvf@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0594 38 83 75</t>
+          <t>06 71 99 62 03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/karting-de-guyane/</t>
+          <t>https://www.macouria.fr/annuaire/equilibre-workout/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1185,7 +1182,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Les écurie de la pointe liberté</t>
+          <t>Espace Gym 2000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1195,17 +1192,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>contact@pointeliberte.fr</t>
+          <t>espace.gym.2000@orange.fr</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0694 41 49 29</t>
+          <t>0694 38 29 09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/les-ecurie-de-la-pointe-liberte/</t>
+          <t>https://www.macouria.fr/annuaire/espace-gym-2000/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1222,7 +1219,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ligue roller &amp; skateboard Guyane</t>
+          <t>Futsal Club de Soula</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1232,17 +1229,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>roller.guyane@orange.fr</t>
+          <t>futsalclubsoula@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0694 24 69 21</t>
+          <t>0694 44 50 03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ligue-roller-skateboard-guyane/</t>
+          <t>https://www.macouria.fr/annuaire/futsal-club-de-soula/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1259,7 +1256,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Macouria Boxing Club</t>
+          <t>Judo Club de Tonate Macouria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1269,17 +1266,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>macouria.boxingclub@gmail.com</t>
+          <t>frederic.munos@cnes.fr</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0694 29 08 48</t>
+          <t>0694 26 46 35 / 0694 13 68 96</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/macouria-boxing-club/</t>
+          <t>https://www.macouria.fr/annuaire/judo-club-de-tonate-macouria/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1296,7 +1293,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Raquette club de Macouria</t>
+          <t>Karting de Guyane</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1306,17 +1303,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rcmacouria@gmail.com</t>
+          <t>m.girard@hotmail.fr</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0694 43 19 21</t>
+          <t>0594 38 83 75</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/raquette-club-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/karting-de-guyane/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1333,7 +1330,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shinto ryû Akido de macouria</t>
+          <t>Les écurie de la pointe liberté</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1343,17 +1340,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>aikido.macouria@yahoo.fr</t>
+          <t>contact@pointeliberte.fr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0694 46 86 46 / 0694 28 50 17</t>
+          <t>0694 41 49 29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/shinto-ryu-akido-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/les-ecurie-de-la-pointe-liberte/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1370,7 +1367,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sprint Club de Macouria</t>
+          <t>Ligue roller &amp; skateboard Guyane</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1380,17 +1377,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>clotairegeorges@gmail.com</t>
+          <t>roller.guyane@orange.fr</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0694 23 45 57</t>
+          <t>0694 24 69 21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/sprint-club-de-macouria/</t>
+          <t>https://www.macouria.fr/annuaire/ligue-roller-skateboard-guyane/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1407,7 +1404,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tonate Académie Art Martiaux (TAAM)</t>
+          <t>Macouria Boxing Club</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1417,17 +1414,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercure.celine@orange.fr</t>
+          <t>macouria.boxingclub@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0694 23 29 15 / 0694 23 91 82</t>
+          <t>0694 29 08 48</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/tonate-academie-art-martiaux-taam/</t>
+          <t>https://www.macouria.fr/annuaire/macouria-boxing-club/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1444,7 +1441,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Union Sportive de Macouria (US Macouria)</t>
+          <t>Raquette club de Macouria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1454,17 +1451,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>usmacouria@gmail.com</t>
+          <t>rcmacouria@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0694 22 93 33</t>
+          <t>0694 43 19 21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/union-sportive-de-macouria-usmacouria/</t>
+          <t>https://www.macouria.fr/annuaire/raquette-club-de-macouria/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1481,32 +1478,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ACS Team Sainte Rose</t>
+          <t>Shinto ryû Akido de macouria</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>association.cstsr@gmail.com</t>
+          <t>aikido.macouria@yahoo.fr</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0694 45 14 04 / 0694 96 76 92</t>
+          <t>0694 46 86 46 / 0694 28 50 17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://www.macouria.fr/annuaire/shinto-ryu-akido-de-macouria/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1518,32 +1515,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACSS Les Orchidées</t>
+          <t>Sprint Club de Macouria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>acsslesorchidees@gmail.com</t>
+          <t>clotairegeorges@gmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0694 03 03 16</t>
+          <t>0694 23 45 57</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://www.macouria.fr/annuaire/sprint-club-de-macouria/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1555,32 +1552,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASC Matoury 88</t>
+          <t>Tonate Académie Art Martiaux (TAAM)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ascmatoury88secretariat@gmail.com</t>
+          <t>mercure.celine@orange.fr</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0694 96 72 82</t>
+          <t>0694 23 29 15 / 0694 23 91 82</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://www.macouria.fr/annuaire/tonate-academie-art-martiaux-taam/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1592,32 +1589,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Association active et sportive</t>
+          <t>Union Sportive de Macouria (US Macouria)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>corahervine1@gmail.com</t>
+          <t>usmacouria@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0694 95 79 86</t>
+          <t>0694 22 93 33</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://www.macouria.fr/annuaire/union-sportive-de-macouria-usmacouria/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1629,32 +1626,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Association des Jeunes de Balata Abriba</t>
+          <t>Association Sportive et Culturelle Vétérans Mananais</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>547712@guyane-foot.fr</t>
+          <t>derby.nd@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0694 93 90 03</t>
+          <t>0694963233</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://mairie-mana.fr/crb_agenda/tournoi-de-petanque-dimanche-14-juillet-2024-a-loccasion-de-lamana-fete/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1666,32 +1663,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Association du Développement Sportif et Culturel</t>
+          <t>Mana Basketball Association</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>patveronique@wanadoo.fr</t>
+          <t>secretariat.manabasket97360@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0694 21 54 48</t>
+          <t>0763007306</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
+          <t>https://mairie-mana.fr/crb_agenda/mana-basketball-association-presente-tournoi-de-basket-edition-happy-christmas/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1703,7 +1700,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Association Kashima Aïkido de Matoury</t>
+          <t>ACS Team Sainte Rose</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1713,12 +1710,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aikido.matoury@outlook.fr</t>
+          <t>association.cstsr@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0694 47 94 21 / 0694 47 34 05</t>
+          <t>0694 45 14 04 / 0694 96 76 92</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,7 +1737,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Association Socio-Culturelle et Sportive pour les Jeunes de Cogneau Lamirande</t>
+          <t>ACSS Les Orchidées</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1750,12 +1747,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sonymontina@gmail.com</t>
+          <t>acsslesorchidees@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0694 45 77 48</t>
+          <t>0694 03 03 16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1777,7 +1774,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Association Sportive Delta</t>
+          <t>ASC Matoury 88</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1787,12 +1784,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>associationsportivedelta@gmail.com</t>
+          <t>ascmatoury88secretariat@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0694 03 14 23 / 0694 92 84 14</t>
+          <t>0694 96 72 82</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1814,7 +1811,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Association Sportive et Culturelle des Vétérans de Matoury</t>
+          <t>Association active et sportive</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1824,12 +1821,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>arsenemathurin973@gmail.com</t>
+          <t>corahervine1@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0694 99 03 21 / 0694 22 10 77</t>
+          <t>0694 95 79 86</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1851,7 +1848,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Association Sportive et Culturelle Loca Central Motors</t>
+          <t>Association des Jeunes de Balata Abriba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1861,17 +1858,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>aslcm@outlook.fr</t>
+          <t>547712@guyane-foot.fr</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0694 42 61 64</t>
+          <t>0694 93 90 03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1888,7 +1885,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Badminton Club de Matoury</t>
+          <t>Association du Développement Sportif et Culturel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1898,17 +1895,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bcm97351@gmail.com</t>
+          <t>patveronique@wanadoo.fr</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>06 37 70 85 12</t>
+          <t>0694 21 54 48</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1925,7 +1922,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BJJ Werdum Guyane</t>
+          <t>Association Kashima Aïkido de Matoury</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1935,17 +1932,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>werdum.guyane@gmail.com</t>
+          <t>aikido.matoury@outlook.fr</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0694 21 68 12</t>
+          <t>0694 47 94 21 / 0694 47 34 05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1962,7 +1959,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Boxing Club de Matoury</t>
+          <t>Association Socio-Culturelle et Sportive pour les Jeunes de Cogneau Lamirande</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1972,17 +1969,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>boxingclub.matoury@gmail.com</t>
+          <t>sonymontina@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0694 43 66 41 / 0694 49 38 80</t>
+          <t>0694 45 77 48</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1999,7 +1996,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Club de Kung Fu et Muay Thaï</t>
+          <t>Association Sportive Delta</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2009,17 +2006,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kungfumuay@yahoo.fr</t>
+          <t>associationsportivedelta@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0694 42 32 00</t>
+          <t>0694 03 14 23 / 0694 92 84 14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2036,7 +2033,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Club École Pétanque de Matoury</t>
+          <t>Association Sportive et Culturelle des Vétérans de Matoury</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2046,17 +2043,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nita.matilde@orange.fr</t>
+          <t>arsenemathurin973@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0694 96 94 91</t>
+          <t>0694 99 03 21 / 0694 22 10 77</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2073,7 +2070,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Coq Roche</t>
+          <t>Association Sportive et Culturelle Loca Central Motors</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2083,17 +2080,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>caro.careme@orange.fr</t>
+          <t>aslcm@outlook.fr</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0694 41 59 29</t>
+          <t>0694 42 61 64</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2110,7 +2107,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Croix du Sud de Matoury</t>
+          <t>Badminton Club de Matoury</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2120,17 +2117,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>croixdusudmatoury@gmail.com</t>
+          <t>bcm97351@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0694 12 51 53</t>
+          <t>06 37 70 85 12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2147,7 +2144,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CSVBM</t>
+          <t>BJJ Werdum Guyane</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2157,17 +2154,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>csvbm97351@gmail.com</t>
+          <t>werdum.guyane@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0694 42 90 83</t>
+          <t>0694 21 68 12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2184,7 +2181,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D'propulsion</t>
+          <t>Boxing Club de Matoury</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2194,17 +2191,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>assodpropulsion@gmail.com</t>
+          <t>boxingclub.matoury@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0694 13 97 33</t>
+          <t>0694 43 66 41 / 0694 49 38 80</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2221,7 +2218,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ecurie La Caracole</t>
+          <t>Club de Kung Fu et Muay Thaï</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2231,17 +2228,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lacaracole973@gmail.com</t>
+          <t>kungfumuay@yahoo.fr</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0694 26 26 97</t>
+          <t>0694 42 32 00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2258,7 +2255,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Energia Pura</t>
+          <t>Club École Pétanque de Matoury</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2268,17 +2265,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>energia.pura.973@gmail.com</t>
+          <t>nita.matilde@orange.fr</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0694 47 70 89</t>
+          <t>0694 96 94 91</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2295,7 +2292,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fitness-Pilates Brenn'fit Club</t>
+          <t>Coq Roche</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2305,12 +2302,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sonia.arnaud5@orange.fr</t>
+          <t>caro.careme@orange.fr</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0694 45 54 89</t>
+          <t>0694 41 59 29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2332,7 +2329,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Futsal Club Balata Matoury</t>
+          <t>Croix du Sud de Matoury</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2342,12 +2339,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>r1arnaud@hotmail.com</t>
+          <t>croixdusudmatoury@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0694 92 73 93</t>
+          <t>0694 12 51 53</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2369,7 +2366,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Horizons Coaching</t>
+          <t>CSVBM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2379,12 +2376,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>horizonscoaching973@outlook.com</t>
+          <t>csvbm97351@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0694 47 70 89</t>
+          <t>0694 42 90 83</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2406,7 +2403,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Judo Club Chiba</t>
+          <t>D'propulsion</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2416,17 +2413,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>judoclubchiba@orange.fr</t>
+          <t>assodpropulsion@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0694 40 67 31</t>
+          <t>0694 13 97 33</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2443,7 +2440,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Judo Club de Matoury</t>
+          <t>Ecurie La Caracole</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2453,17 +2450,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>faubert.charles@wanadoo.fr</t>
+          <t>lacaracole973@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0694 23 27 03</t>
+          <t>0694 26 26 97</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2480,7 +2477,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Keumgang Dojang</t>
+          <t>Energia Pura</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2490,17 +2487,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>taekwondo_guyane@yahoo.fr</t>
+          <t>energia.pura.973@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0694 20 05 96</t>
+          <t>0694 47 70 89</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2517,7 +2514,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>La Kaz Guyane</t>
+          <t>Fitness-Pilates Brenn'fit Club</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2527,17 +2524,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>joseph.reginal@hotmail.fr</t>
+          <t>sonia.arnaud5@orange.fr</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0694 44 51 21</t>
+          <t>0694 45 54 89</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2554,7 +2551,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marsouins de Matoury</t>
+          <t>Futsal Club Balata Matoury</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2564,17 +2561,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>marsouins.matoury973@gmail.com</t>
+          <t>r1arnaud@hotmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0694 08 98 27 / 0694 26 76 03 / 0694 21 32 50</t>
+          <t>0694 92 73 93</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2591,7 +2588,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Matoury Escrime</t>
+          <t>Horizons Coaching</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2601,17 +2598,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>clubmatouryescrime@gmail.com</t>
+          <t>horizonscoaching973@outlook.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0694 02 77 82</t>
+          <t>0694 47 70 89</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2628,7 +2625,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Myob</t>
+          <t>Judo Club Chiba</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2638,12 +2635,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>assomyob@gmail.com</t>
+          <t>judoclubchiba@orange.fr</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>06 45 07 40 19</t>
+          <t>0694 40 67 31</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2665,7 +2662,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NST 51 Futsal</t>
+          <t>Judo Club de Matoury</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2675,12 +2672,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>n.s.t.51futsal@gmail.com</t>
+          <t>faubert.charles@wanadoo.fr</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0694 15 55 50</t>
+          <t>0694 23 27 03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2702,7 +2699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Okinawa Karaté Do</t>
+          <t>Keumgang Dojang</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2712,12 +2709,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sergelhn@yahoo.fr</t>
+          <t>taekwondo_guyane@yahoo.fr</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0694 26 36 83</t>
+          <t>0694 20 05 96</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2739,7 +2736,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Shines Academy</t>
+          <t>La Kaz Guyane</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2749,17 +2746,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>theshinesacademy@gmail.com</t>
+          <t>joseph.reginal@hotmail.fr</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>07 60 79 09 22</t>
+          <t>0694 44 51 21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2776,7 +2773,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tennis Club de Matoury</t>
+          <t>Marsouins de Matoury</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2786,17 +2783,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>tennis.matoury@gmail.com</t>
+          <t>marsouins.matoury973@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0694 21 71 01</t>
+          <t>0694 08 98 27 / 0694 26 76 03 / 0694 21 32 50</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2813,7 +2810,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tontons &amp; Taties Flingueurs GUY-MAR-GUA</t>
+          <t>Matoury Escrime</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2823,17 +2820,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ttflingueurs973@gmail.com</t>
+          <t>clubmatouryescrime@gmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0694 45 76 10</t>
+          <t>0694 02 77 82</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2850,7 +2847,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Union Sportive de Matoury</t>
+          <t>Myob</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2860,17 +2857,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>usmatouryfootball@gmail.com</t>
+          <t>assomyob@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0694 21 86 35</t>
+          <t>06 45 07 40 19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2887,7 +2884,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>USM Hand-ball</t>
+          <t>NST 51 Futsal</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2897,17 +2894,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>anne-marie.eric@orange.fr</t>
+          <t>n.s.t.51futsal@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0694 21 33 44</t>
+          <t>0694 15 55 50</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2924,7 +2921,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Étoile de Matoury</t>
+          <t>Okinawa Karaté Do</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2934,17 +2931,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>etoile.matoury@gmail.com</t>
+          <t>sergelhn@yahoo.fr</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0694 21 21 77</t>
+          <t>0694 26 36 83</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2961,32 +2958,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ASCO</t>
+          <t>Shines Academy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>580565@guyane-foot.fr</t>
+          <t>theshinesacademy@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>06 94 47 96 90</t>
+          <t>07 60 79 09 22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2998,32 +2995,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ASL Maroni</t>
+          <t>Tennis Club de Matoury</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>aslmaroni@gmail.com</t>
+          <t>tennis.matoury@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>06 94 28 58 99</t>
+          <t>0694 21 71 01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3035,32 +3032,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Association centre équestre kawale</t>
+          <t>Tontons &amp; Taties Flingueurs GUY-MAR-GUA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kawaleclub@gmail.com</t>
+          <t>ttflingueurs973@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>06 94 12 51 25</t>
+          <t>0694 45 76 10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3072,32 +3069,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aïkido Jutsu Du Maroni</t>
+          <t>Union Sportive de Matoury</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>aikido.maroni@outlook.fr</t>
+          <t>usmatouryfootball@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>06 94 47 94 21</t>
+          <t>0694 21 86 35</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3109,32 +3106,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Corps et Cultures en Mouvement</t>
+          <t>USM Hand-ball</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>corpsetculturesenmouvement@gmail.com</t>
+          <t>anne-marie.eric@orange.fr</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>06 94 09 66 65</t>
+          <t>0694 21 33 44</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=5</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3146,32 +3143,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COSMA Basketball</t>
+          <t>Étoile de Matoury</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>cosmabasketball@gmail.com</t>
+          <t>etoile.matoury@gmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>06 94 43 10 19</t>
+          <t>0694 21 21 77</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3183,32 +3180,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COSMA Boxing Club</t>
+          <t>Association Yanarun (semi-marathon de Rémire-Montjoly)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>cosmaboxingclub@orange.fr</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>06 94 20 92 15</t>
-        </is>
-      </c>
+          <t>yanarunners@gmail.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://remire-montjoly.fr/crb_event/3e-edition-du-semi-marathon-de-eemire-montjoly/</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3220,7 +3213,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COSMA Canoë Kayak</t>
+          <t>ASCO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3230,17 +3223,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>president@kayakmaroni.fr</t>
+          <t>580565@guyane-foot.fr</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>06 94 48 87 27</t>
+          <t>06 94 47 96 90</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3257,7 +3250,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COSMA Foot</t>
+          <t>ASL Maroni</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3267,17 +3260,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>bakabushi@orange.fr</t>
+          <t>aslmaroni@gmail.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>06 94 12 35 57</t>
+          <t>06 94 28 58 99</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3294,7 +3287,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COSMA HandBall</t>
+          <t>Association centre équestre kawale</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3304,13 +3297,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>cosmasectionhandball97320@gmail.com</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>kawaleclub@gmail.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>06 94 12 51 25</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3327,7 +3324,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COSMA Judo</t>
+          <t>Aïkido Jutsu Du Maroni</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3337,17 +3334,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>julien.racaniere@gmail.com</t>
+          <t>aikido.maroni@outlook.fr</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>06 94 28 18 98</t>
+          <t>06 94 47 94 21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3364,7 +3361,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COSMA Karate club</t>
+          <t>Corps et Cultures en Mouvement</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3374,12 +3371,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>allebejeanpaul@gmail.com</t>
+          <t>corpsetculturesenmouvement@gmail.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>06 94 42 34 78</t>
+          <t>06 94 09 66 65</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3401,7 +3398,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COSMA Powerlifting</t>
+          <t>COSMA Basketball</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3411,12 +3408,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>cosmapowerlifting@gmail.com</t>
+          <t>cosmabasketball@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>06 94 41 34 04</t>
+          <t>06 94 43 10 19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3438,7 +3435,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>COSMA Rugby</t>
+          <t>COSMA Boxing Club</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3448,12 +3445,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>cosma-rugby@outlook.fr</t>
+          <t>cosmaboxingclub@orange.fr</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>06 70 18 40 86</t>
+          <t>06 94 20 92 15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3475,7 +3472,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COSMA Tennis</t>
+          <t>COSMA Canoë Kayak</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3485,17 +3482,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>juliej.57@hotmail.fr</t>
+          <t>president@kayakmaroni.fr</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>06 27 56 35 70</t>
+          <t>06 94 48 87 27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3512,7 +3509,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COSMA Tennis de table</t>
+          <t>COSMA Foot</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3522,17 +3519,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>cosmatt97320@gmail.com</t>
+          <t>bakabushi@orange.fr</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>06 94 21 18 53</t>
+          <t>06 94 12 35 57</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3549,7 +3546,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COSMA Volley</t>
+          <t>COSMA HandBall</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3559,17 +3556,13 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>cosmavb19@gmail.com</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>06 94 99 35 41</t>
-        </is>
-      </c>
+          <t>cosmasectionhandball97320@gmail.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3586,7 +3579,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Coumarou Club Maroni</t>
+          <t>COSMA Judo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3596,17 +3589,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>coumarou.maroni@gmail.com</t>
+          <t>julien.racaniere@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>06 94 43 30 20</t>
+          <t>06 94 28 18 98</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3623,7 +3616,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EJB Balaté</t>
+          <t>COSMA Karate club</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3633,17 +3626,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ejbalate.guyane2009@gmail.com</t>
+          <t>allebejeanpaul@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>06 94 21 07 90</t>
+          <t>06 94 42 34 78</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3660,7 +3653,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Graines D’Acrobates</t>
+          <t>COSMA Powerlifting</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3670,17 +3663,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>gdacrobates@orange.fr</t>
+          <t>cosmapowerlifting@gmail.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>06 94 20 27 86</t>
+          <t>06 94 41 34 04</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3697,7 +3690,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Happy Fit</t>
+          <t>COSMA Rugby</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3707,17 +3700,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>happyfit973@gmail.com</t>
+          <t>cosma-rugby@outlook.fr</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>06 94 24 97 78</t>
+          <t>06 70 18 40 86</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=4</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3734,7 +3727,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Maroni Raquette</t>
+          <t>COSMA Tennis</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3744,17 +3737,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>beatriceleadys.boulot@gmail.com</t>
+          <t>juliej.57@hotmail.fr</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>06 94 46 96 87</t>
+          <t>06 27 56 35 70</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3771,7 +3764,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maroni Tir</t>
+          <t>COSMA Tennis de table</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3781,17 +3774,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>cosmatir@yahoo.fr</t>
+          <t>cosmatt97320@gmail.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>06 94 43 94 76</t>
+          <t>06 94 21 18 53</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3808,7 +3801,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ouest Sport Guyane</t>
+          <t>COSMA Volley</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3818,17 +3811,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ouest.sportguyane@gmail.com</t>
+          <t>cosmavb19@gmail.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>06 94 96 99 95</t>
+          <t>06 94 99 35 41</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3845,7 +3838,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Puma athletic club maroni</t>
+          <t>Coumarou Club Maroni</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3855,17 +3848,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>pumaathleticclubdumaroni@gmail.com</t>
+          <t>coumarou.maroni@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>06 94 43 75 84</t>
+          <t>06 94 43 30 20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3882,7 +3875,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PYON WON TAEKWONDO</t>
+          <t>EJB Balaté</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3892,17 +3885,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>rchinama@yahoo.com</t>
+          <t>ejbalate.guyane2009@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>06 94 37 17 66</t>
+          <t>06 94 21 07 90</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3919,7 +3912,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RC MARONI</t>
+          <t>Graines D’Acrobates</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3929,17 +3922,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>racingclub.maroni@gmail.com</t>
+          <t>gdacrobates@orange.fr</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>06 94 15 16 19</t>
+          <t>06 94 20 27 86</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3956,7 +3949,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Roller Skating Maroni</t>
+          <t>Happy Fit</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3966,17 +3959,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>roller.skating.maroni@ligue-roller-skateboard-maroni.fr</t>
+          <t>happyfit973@gmail.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>06 94 16 95 44</t>
+          <t>06 94 24 97 78</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3993,7 +3986,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vamos Jogar CAPOEIRA</t>
+          <t>Maroni Raquette</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4003,17 +3996,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>vjcapoeira973@gmail.com</t>
+          <t>beatriceleadys.boulot@gmail.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>06 94 26 78 25</t>
+          <t>06 94 46 96 87</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4030,7 +4023,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Velo Club du Maroni</t>
+          <t>Maroni Tir</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4040,17 +4033,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>vcm-973@hotmail.fr</t>
+          <t>cosmatir@yahoo.fr</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>06 94 44 43 56</t>
+          <t>06 94 43 94 76</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4067,7 +4060,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vélo club du maroni</t>
+          <t>Ouest Sport Guyane</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4077,17 +4070,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>lorens97320@gmail.com</t>
+          <t>ouest.sportguyane@gmail.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>06 94 44 43 56</t>
+          <t>06 94 96 99 95</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4104,328 +4097,328 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ass. scrab’Attitude</t>
+          <t>Puma athletic club maroni</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>dauphin.guilaine@wanadoo.fr</t>
+          <t>pumaathleticclubdumaroni@gmail.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0694 23 84 32 / 0594 38 83 69</t>
+          <t>06 94 43 75 84</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ass-scrabattitude/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Macouria club radio commande</t>
+          <t>PYON WON TAEKWONDO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>steeve.constable973@gmail.com</t>
+          <t>rchinama@yahoo.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0694 21 12 04</t>
+          <t>06 94 37 17 66</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/macouria-club-radio-commande/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>THÉÂTRE DE MACOURIA</t>
+          <t>RC MARONI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>t.ramkaran@theatre-de-macouria.com</t>
+          <t>racingclub.maroni@gmail.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>06 94 16 44 93 06 94 22 95 04</t>
+          <t>06 94 15 16 19</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/theatre-de-macouria/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ÉCOLE DE MUSIQUE : MACOURIA MUSIQUE</t>
+          <t>Roller Skating Maroni</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>emdtic1@gmail.com</t>
+          <t>roller.skating.maroni@ligue-roller-skateboard-maroni.fr</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>06 94 24 43 02</t>
+          <t>06 94 16 95 44</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ecole-de-musique-macouria-musique/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ACMS ZOUTI</t>
+          <t>Vamos Jogar CAPOEIRA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>marlenecoco@orange.fr</t>
+          <t>vjcapoeira973@gmail.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0694 21 34 22</t>
+          <t>06 94 26 78 25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AHINA'MA</t>
+          <t>Velo Club du Maroni</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ahinamadanse@hotmail.fr</t>
+          <t>vcm-973@hotmail.fr</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0594 31 46 92 / 0694 22 06 19</t>
+          <t>06 94 44 43 56</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMARYLIS</t>
+          <t>Vélo club du maroni</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>association.amaryllis@hotmail.fr</t>
+          <t>lorens97320@gmail.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0594 35 27 76 / 0694 38 35 12</t>
+          <t>06 94 44 43 56</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>APHABA</t>
+          <t>Les Ybis des Savanes (volley-ball)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Sinnamary</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>lealnadia@wanadoo.fr</t>
+          <t>lesybisdessavanes973@gmail.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0594 35 32 32 / 0694 41 46 74</t>
+          <t>0694 16 04 02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://www.ville-sinnamary.fr/actualite/volley-ball-un-nouveau-club-pour-les-savanes/</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>loisirs/culture</t>
+          <t>sport</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ARAWAKS DE ST ROSE DE LIMA</t>
+          <t>Arist Prod</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>charleswingarde@gmail.com</t>
+          <t>aristguyane@hotmail.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0694 23 42 41</t>
+          <t>06.94.23.80.15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4437,32 +4430,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ART'BRE OR ET SENS</t>
+          <t>AS Caraïbe Serv's</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>arbreoretsens@hotmail.fr</t>
+          <t>as-caraibe.serv@hotmail.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0694 24 37 59 / 0594 37 93 68</t>
+          <t>0694 26 37 29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4474,32 +4467,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BILEMBI</t>
+          <t>Association Les Pas Mêlés (tiers-lieu L'Abattis)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>bitegue@wanadoo.fr</t>
+          <t>lespasmeles@gmail.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0594 35 39 10 / 0694 41 24 82</t>
+          <t>06 24 59 67 68</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4511,32 +4504,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Club Astucieux de Matoury</t>
+          <t>Association Pomme d'Amour</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>astucieuxclub@orange.fr</t>
+          <t>ac-pommedamour@hotmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0694 42 71 62</t>
+          <t>0694.95.19.78</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4548,32 +4541,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DOMINO MASTER</t>
+          <t>Les p'tits bambousiens</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>elpistolero59@gmail.com</t>
+          <t>lespetitsbambousiens@gmail.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0694 92 50 18</t>
+          <t>0694 93 51 84</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4585,32 +4578,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EAST INDIAN CULTURAL DE GUYANE</t>
+          <t>Team Baromètre</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>nandalall@hotmail.com</t>
+          <t>teambarometre973@gmail.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0694 90 83 35</t>
+          <t>0694.02.24.67</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4622,28 +4615,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GACID</t>
+          <t>Tourépé (centre de loisirs)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Cayenne</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>gacid973@orange.fr</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>secretariat@tourepe-loisirs.fr</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0694 987 016 / 0694 229 233</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4655,32 +4652,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JET 7 GHETTO FAMILY</t>
+          <t>Association MKT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jet7ghettofamily@gmail.com</t>
+          <t>mkt973@gmail.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0694 98 03 50</t>
+          <t>0694 47 84 30 / 0694 03 73 47</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/espri-konvwe-a-savann/</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4692,32 +4689,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>K' NEL</t>
+          <t>Color Tango</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>naiagf@yahoo.fr</t>
+          <t>contact@colortango.org</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0694 42 44 29</t>
+          <t>0694 90 98 62</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/agenda/fete-de-la-musique-2025/</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4729,32 +4726,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KAYENNO</t>
+          <t>Empreinte Colorée</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>associationkayenno@mediaserv.net</t>
+          <t>asso.empreinte.coloree@outlook.fr</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0594 35 68 55</t>
+          <t>0694 12 07 69 / 0694 49 13 53</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/agenda/atelier-theatre-forum/</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4766,32 +4763,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KOGNOTOPIA</t>
+          <t>Live Your Dreams</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>kognotopia@laposte.net</t>
+          <t>assolyd@outlook.fr</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0694 26 52 29 / 0694 90 38 59</t>
+          <t>0694 48 72 39</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/wp-content/uploads/2025/05/AGENDA-Aout-2025_250731_112622.pdf</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4803,32 +4800,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KONBIT</t>
+          <t>Mouv'lavie</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>marosecuperlier@msn.com</t>
+          <t>mouvlavie@gmail.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0694 22 34 26</t>
+          <t>+594 694 20 96 66</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/ateliers-de-couture-special-fete-des-meres/</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4840,32 +4837,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LA POMPADOUR</t>
+          <t>YUJKAYA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Kourou</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>lapompadour.marly@orange.fr</t>
+          <t>yujkaya@gmail.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0594 35 88 50 / 0694 23 35 28</t>
+          <t>07 77 06 41 78</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
+          <t>https://www.ville-kourou.fr/wp-content/uploads/2025/05/AGENDA-Aout-2025_250731_112622.pdf</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4877,32 +4874,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LILLIPUT SCHOOL</t>
+          <t>Ass. scrab’Attitude</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lilliput.school@orange.fr</t>
+          <t>dauphin.guilaine@wanadoo.fr</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0594 35 68 10</t>
+          <t>0694 23 84 32 / 0594 38 83 69</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
+          <t>https://www.macouria.fr/annuaire/ass-scrabattitude/</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4914,32 +4911,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LIVITY ART CREW</t>
+          <t>Macouria club radio commande</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>livity973@hotmail.fr</t>
+          <t>steeve.constable973@gmail.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0694 20 66 30 / 0694 23 63 28</t>
+          <t>0694 21 12 04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
+          <t>https://www.macouria.fr/annuaire/macouria-club-radio-commande/</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4951,32 +4948,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MI TWA MI TA MWEN</t>
+          <t>THÉÂTRE DE MACOURIA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>steve.2@wanadoo.fr</t>
+          <t>t.ramkaran@theatre-de-macouria.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0694 43 15 43</t>
+          <t>06 94 16 44 93 06 94 22 95 04</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
+          <t>https://www.macouria.fr/annuaire/theatre-de-macouria/</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4988,32 +4985,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MOFAYA</t>
+          <t>ÉCOLE DE MUSIQUE : MACOURIA MUSIQUE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Macouria</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>toridj973@gmail.com</t>
+          <t>emdtic1@gmail.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0694 24 69 14</t>
+          <t>06 94 24 43 02</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
+          <t>https://www.macouria.fr/annuaire/ecole-de-musique-macouria-musique/</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5025,32 +5022,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ORCHIDÉES</t>
+          <t>Arty Yana</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>agnisa21@gmail.com</t>
+          <t>arty.yana973@gmail.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0694 04 21 04 / 0694 03 03 16</t>
+          <t>06 24 85 80 01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
+          <t>https://mairie-mana.fr/crb_agenda/vide-carbet-centre-social-makandra/</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5062,32 +5059,28 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STREET SOLDIERS</t>
+          <t>Association Anophèle</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Matoury</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>lil-jho@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>0694 46 47 70 / 0694 94 09 32</t>
-        </is>
-      </c>
+          <t>lanophele@gmail.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=5</t>
+          <t>https://mairie-mana.fr/crb_agenda/concours-anophoto-2024/</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5099,32 +5092,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AOL PaintBall</t>
+          <t>Centre Chorégraphique Pépinière</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>notimestudio@live.fr</t>
+          <t>ccp97320@gmail.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>06 94 26 64 97</t>
+          <t>0637720970</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://mairie-mana.fr/crb_agenda/inscription-cours-de-danse-centre-social-makandra/</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5136,32 +5129,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Association Jeunes Sans Limites</t>
+          <t>Lavi Dan Bwa</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jeunessanslimites@gmail.com</t>
+          <t>association.lavidanbwa@gmail.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>06 94 03 06 93</t>
+          <t>+594 694 42 03 27 / 0699 26 98 61 / 0694 04 54 09</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://mairie-mana.fr/festival-busi-konde-sama-a-mana/</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5173,32 +5166,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Association pour la découverte de la nature en Guyane (ADNG)</t>
+          <t>Le Gospel Connecté</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>adng.guyane@gmail.com</t>
+          <t>legospelconnect@gmail.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>06 94 91 14 34</t>
+          <t>0694 94 47 98 / 0594 23 07 18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://mairie-mana.fr/crb_agenda/concert-de-gospel-hans-edouard-special-fete-meres/</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5210,32 +5203,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ATAM</t>
+          <t>ACMS ZOUTI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>juste.romain@hotmail.fr</t>
+          <t>marlenecoco@orange.fr</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>06 94 44 66 43</t>
+          <t>0694 21 34 22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5247,32 +5240,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Atelier Vidéo Multimédia (AVM)</t>
+          <t>AHINA'MA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>info@poleimagemaroni.org</t>
+          <t>ahinamadanse@hotmail.fr</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0594 27 65 18</t>
+          <t>0594 31 46 92 / 0694 22 06 19</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5284,32 +5277,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Atipa Record Musik Label</t>
+          <t>AMARYLIS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>atiparecord@gmail.com</t>
+          <t>association.amaryllis@hotmail.fr</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>06 94 90 56 17</t>
+          <t>0594 35 27 76 / 0694 38 35 12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5321,32 +5314,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Bois Canon</t>
+          <t>APHABA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>cafeassoslm@mailo.com</t>
+          <t>lealnadia@wanadoo.fr</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>06 94 23 93 20</t>
+          <t>0594 35 32 32 / 0694 41 46 74</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5358,32 +5351,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Carbet des Associations</t>
+          <t>ARAWAKS DE ST ROSE DE LIMA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>carbetdesassociations973@gmail.com</t>
+          <t>charleswingarde@gmail.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>06 94 09 08 07</t>
+          <t>0694 23 42 41</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5395,32 +5388,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Déco Passion</t>
+          <t>ART'BRE OR ET SENS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>bridget.boutin@orange.fr</t>
+          <t>arbreoretsens@hotmail.fr</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>06 94 41 09 89</t>
+          <t>0694 24 37 59 / 0594 37 93 68</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5432,32 +5425,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Freshblood</t>
+          <t>BILEMBI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>freshblood.infos@gmail.com</t>
+          <t>bitegue@wanadoo.fr</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>06 94 12 92 64</t>
+          <t>0594 35 39 10 / 0694 41 24 82</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5469,32 +5462,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ghetto Black Music</t>
+          <t>Club Astucieux de Matoury</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ghettoblackmusic@gmail.com</t>
+          <t>astucieuxclub@orange.fr</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>06 94 04 08 89</t>
+          <t>0694 42 71 62</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-clubs-sportifs?1058753f_page=2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5506,32 +5499,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>La Maro’jeux</t>
+          <t>DOMINO MASTER</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>lamarojeux@gmail.com</t>
+          <t>elpistolero59@gmail.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>06 94 43 18 82</t>
+          <t>0694 92 50 18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5543,32 +5536,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Latitude Cirque</t>
+          <t>EAST INDIAN CULTURAL DE GUYANE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>latitudecirque@gmail.com</t>
+          <t>nandalall@hotmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>06 94 45 98 17</t>
+          <t>0694 90 83 35</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5580,32 +5573,28 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Les 2 roues de l’ouest</t>
+          <t>GACID</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>maservais@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>06 94 41 68 80</t>
-        </is>
-      </c>
+          <t>gacid973@orange.fr</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=2</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5617,28 +5606,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Les Lianes Musicales</t>
+          <t>JET 7 GHETTO FAMILY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>tangouchka@hotmail.fr</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>jet7ghettofamily@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0694 98 03 50</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5650,32 +5643,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Malabarouf</t>
+          <t>K' NEL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>malarouf@gmail.com</t>
+          <t>naiagf@yahoo.fr</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>06 94 95 36 12</t>
+          <t>0694 42 44 29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5687,32 +5680,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Manifact – LA KAZLAB</t>
+          <t>KAYENNO</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>contact@manifact.org</t>
+          <t>associationkayenno@mediaserv.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0594 59 26 66</t>
+          <t>0594 35 68 55</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5724,32 +5717,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ONDOO FENI</t>
+          <t>KOGNOTOPIA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ondoofen@gmail.com</t>
+          <t>kognotopia@laposte.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>06 94 03 40 93</t>
+          <t>0694 26 52 29 / 0694 90 38 59</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5761,32 +5754,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ouest Guyane Animation</t>
+          <t>KONBIT</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ouestguyaneanimation@gmail.com</t>
+          <t>marosecuperlier@msn.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>06 94 22 58 49</t>
+          <t>0694 22 34 26</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5798,32 +5791,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ouest Union</t>
+          <t>LA POMPADOUR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>fiersma973@gmail.com</t>
+          <t>lapompadour.marly@orange.fr</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>06 94 03 77 19</t>
+          <t>0594 35 88 50 / 0694 23 35 28</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=3</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5835,32 +5828,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Vent d’Ouest</t>
+          <t>LILLIPUT SCHOOL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>president.ventdouest@gmail.com</t>
+          <t>lilliput.school@orange.fr</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>06 94 36 28 98</t>
+          <t>0594 35 68 10</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5872,32 +5865,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WYBOO</t>
+          <t>LIVITY ART CREW</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>assowyboo@gmail.com</t>
+          <t>livity973@hotmail.fr</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>06 94 13 55 56</t>
+          <t>0694 20 66 30 / 0694 23 63 28</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=10</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5909,32 +5902,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Yukulim</t>
+          <t>MI TWA MI TA MWEN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>mikkemanewamo@gmail.com</t>
+          <t>steve.2@wanadoo.fr</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>06 94 23 40 79</t>
+          <t>0694 43 15 43</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=10</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5946,377 +5939,373 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A Wi Sani</t>
+          <t>MOFAYA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jokedikan@gmail.com</t>
+          <t>toridj973@gmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>06 94 06 18 56</t>
+          <t>0694 24 69 14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Association de Tous les Ages du Maroni (ATAM)</t>
+          <t>ORCHIDÉES</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>atam973@orange.fr</t>
+          <t>agnisa21@gmail.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>06 94 24 26 70</t>
+          <t>0694 04 21 04 / 0694 03 03 16</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=4</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Association des Parents et Amis des Déficients Auditifs de Guyane (APADAG)</t>
+          <t>STREET SOLDIERS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Matoury</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>oona.goet@apadag.org</t>
+          <t>lil-jho@hotmail.com</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0594 34 28 59</t>
+          <t>0694 46 47 70 / 0694 94 09 32</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://www.ville-matoury.fr/nos-associations-culturelles?d4883692_page=5</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Association Fourka</t>
+          <t>Association Aux Deux Moustiques</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>asso.fourka-slm@orange.fr</t>
+          <t>auxdeuxmoustiques@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0594 34 35 55</t>
+          <t>0694 281885</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://remire-montjoly.fr/crb_event/ateliers-aux-deux-moustiques/</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Association Guyane Accompagnements Développement Jalonnes (GADJ)</t>
+          <t>Association Zoukouyanyan</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>gadj973@gmail.com</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>06 94 24 69 14</t>
-        </is>
-      </c>
+          <t>diffusion@zoukouyanyan.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://remire-montjoly.fr/crb_event/mille-guyanes/</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Association pour la Promotion de la Citoyenneté des Jeunes et des Familles (APCJF)</t>
+          <t>Association Zoukouyanyan (Maison du conte)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>apcjf.guyane@gmail.com</t>
+          <t>maisonduconte@zoukouyanyan.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>06 94 22 10 26</t>
+          <t>0694 019636</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+          <t>https://remire-montjoly.fr/crb_event/blanche-neige-fille-dafrique/</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Centre d’Accueil et d’Accompagnement à la Réduction des Risques pour Usagers (CAARRUD)</t>
+          <t>Club de Littérature en Mémoire</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>caarudsl@akatij.fr</t>
+          <t>patricia.laurencine@gmail.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0594 34 10 04</t>
+          <t>06 61 53 14 63</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Communauté thérapeutique pour femmes en ambulatoire</t>
+          <t>Compagnie Yanart T</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ctsl@akatij.fr</t>
+          <t>cie.yat973@gmail.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0594 34 86 31</t>
+          <t>0694 40 43 42</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ebène</t>
+          <t>Doubout Collectif (théâtre Testament du Kaptif)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>yolaineburke973@orange.fr</t>
+          <t>testamentdukaptif2022@gmail.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0594 34 42 40</t>
+          <t>0694 488002</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://remire-montjoly.fr/crb_event/theatre-testament-du-kaptif/</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ensemble on va loin</t>
+          <t>Herbe Association (La liberté de lire)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Saint-Laurent-du-Maroni</t>
+          <t>Rémire-Montjoly</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>romayalu11@gmail.com</t>
+          <t>herbe.association@gmail.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>06 94 41 09 89</t>
+          <t>06 76 60 32 48</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://remire-montjoly.fr/crb_event/la-liberte-de-lire/</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Entraide Chiens Chats du Maroni</t>
+          <t>AOL PaintBall</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6326,17 +6315,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>entraidechienschatsmaroni@gmail.com</t>
+          <t>notimestudio@live.fr</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>06 94 12 22 30</t>
+          <t>06 94 26 64 97</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6346,14 +6335,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mama Bobi</t>
+          <t>Association Jeunes Sans Limites</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6363,17 +6352,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>mamabobi@wanadoo.fr</t>
+          <t>jeunessanslimites@gmail.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0594 34 39 17</t>
+          <t>06 94 03 06 93</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6383,14 +6372,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PIKI PIPIT TRANSI ZEN (PPTZ)</t>
+          <t>Association pour la découverte de la nature en Guyane (ADNG)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6400,13 +6389,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>pptz973.md@gmail.com</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>adng.guyane@gmail.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>06 94 91 14 34</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6416,14 +6409,14 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S’identifier, S’élever et Réussir en Guyane (SSR)</t>
+          <t>ATAM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6433,17 +6426,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>association@ssrguyane.fr</t>
+          <t>juste.romain@hotmail.fr</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>06 33 62 32 34</t>
+          <t>06 94 44 66 43</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6453,14 +6446,14 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Wi anga wi – Espace de Vie Sociale Les Ecoles</t>
+          <t>Atelier Vidéo Multimédia (AVM)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6470,17 +6463,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>asso.waw973@gmail.com</t>
+          <t>info@poleimagemaroni.org</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>06 94 02 95 80</t>
+          <t>0594 27 65 18</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6490,276 +6483,2538 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>solidarité</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ADER</t>
+          <t>Atipa Record Musik Label</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ader.kourou@orange.fr</t>
+          <t>atiparecord@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>06 94 44 40 67</t>
+          <t>06 94 90 56 17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/ader/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AKATIJ</t>
+          <t>Bois Canon</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>f.poulain@akatij.fr</t>
+          <t>cafeassoslm@mailo.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>06 94 95 77 90</t>
+          <t>06 94 23 93 20</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/akatij/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ASSOCIATION PERFA973</t>
+          <t>Carbet des Associations</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>guillaume.perfa973@gmail.com</t>
+          <t>carbetdesassociations973@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>07 81 31 66 97</t>
+          <t>06 94 09 08 07</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/association-perfa973/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LA LOUPIOTE</t>
+          <t>Déco Passion</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>laloupiote973@gmail.com</t>
+          <t>bridget.boutin@orange.fr</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>06 94 40 13 19</t>
+          <t>06 94 41 09 89</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/la-loupiote/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MACAO GUYANE</t>
+          <t>Freshblood</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>guyanemacao@gmail.com</t>
+          <t>freshblood.infos@gmail.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>06 94 91 04 35 06 94 01 93 81</t>
+          <t>06 94 12 92 64</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/macao-guyane/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TOE LOBIE</t>
+          <t>Ghetto Black Music</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Macouria</t>
+          <t>Saint-Laurent-du-Maroni</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>toelobie@laposte.net</t>
+          <t>ghettoblackmusic@gmail.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>06 94 46 88 37</t>
+          <t>06 94 04 08 89</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.macouria.fr/annuaire/toe-lobie/</t>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>loisirs/culture</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>La Maro’jeux</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>lamarojeux@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>06 94 43 18 82</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Latitude Cirque</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>latitudecirque@gmail.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>06 94 45 98 17</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Les 2 roues de l’ouest</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>maservais@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>06 94 41 68 80</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Les Lianes Musicales</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>tangouchka@hotmail.fr</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Malabarouf</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>malarouf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>06 94 95 36 12</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=6</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Manifact – LA KAZLAB</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>contact@manifact.org</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0594 59 26 66</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ONDOO FENI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ondoofen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>06 94 03 40 93</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ouest Guyane Animation</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ouestguyaneanimation@gmail.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>06 94 22 58 49</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Ouest Union</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>fiersma973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>06 94 03 77 19</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Vent d’Ouest</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>president.ventdouest@gmail.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>06 94 36 28 98</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>WYBOO</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>assowyboo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>06 94 13 55 56</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=10</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Yukulim</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>mikkemanewamo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>06 94 23 40 79</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=10</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Les Amis de Paulin CLET</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sinnamary</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>associationlesamisdepaulinclet@gmail.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.ville-sinnamary.fr/actualite/sinnamary-bel-peyi-la-poesie-en-fete/</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ADER Guyane (antenne de Kourou)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Kourou</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ader.kourou@gmail.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0694 44 40 67</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.ville-kourou.fr/a-la-rencontre-de-nos-associations-ader-guyane/</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Association ladiesmoo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Kourou</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ladiesmoo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.ville-kourou.fr/fete-des-voisins-2026/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DAAC Guyane</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>c.mathurin@daacguyane.org</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>06 94 42 15 63</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/paged-2/6/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Drépaguyane</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>drepaguyane@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0694 27 58 57</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/agenda/drepanocytose/</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Association Awono La'a Yana</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>awonolayana2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0694 213520</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/lart-pour-soutenir-les-cancers-pediatriques/</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Association Fibromyalgie de la Guyane</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>assosfibromyalgieguyane@gmail.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0694 255546</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/fibromyalgie-lassociation-fibromyalgie-de-la-guyane-a-votre-ecoute/</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Event &amp; B</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>eventb973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0694 23 80 05</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SERAC Pôle Guyane</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>guyane@serac-asso.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0694 44 66 62</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>A Wi Sani</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>jokedikan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>06 94 06 18 56</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Association de Tous les Ages du Maroni (ATAM)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>atam973@orange.fr</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>06 94 24 26 70</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Association des Parents et Amis des Déficients Auditifs de Guyane (APADAG)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>oona.goet@apadag.org</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0594 34 28 59</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Association Fourka</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>asso.fourka-slm@orange.fr</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>0594 34 35 55</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Association Guyane Accompagnements Développement Jalonnes (GADJ)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>gadj973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>06 94 24 69 14</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Association pour la Promotion de la Citoyenneté des Jeunes et des Familles (APCJF)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>apcjf.guyane@gmail.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>06 94 22 10 26</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=2</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Centre d’Accueil et d’Accompagnement à la Réduction des Risques pour Usagers (CAARRUD)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>caarudsl@akatij.fr</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0594 34 10 04</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Communauté thérapeutique pour femmes en ambulatoire</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ctsl@akatij.fr</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>0594 34 86 31</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=3</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Ebène</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>yolaineburke973@orange.fr</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0594 34 42 40</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Ensemble on va loin</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>romayalu11@gmail.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>06 94 41 09 89</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Entraide Chiens Chats du Maroni</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>entraidechienschatsmaroni@gmail.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>06 94 12 22 30</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=5</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Mama Bobi</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>mamabobi@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0594 34 39 17</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=7</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PIKI PIPIT TRANSI ZEN (PPTZ)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>pptz973.md@gmail.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>S’identifier, S’élever et Réussir en Guyane (SSR)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>association@ssrguyane.fr</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>06 33 62 32 34</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=8</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Wi anga wi – Espace de Vie Sociale Les Ecoles</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-du-Maroni</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>asso.waw973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>06 94 02 95 80</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.saintlaurentdumaroni.fr/association/?sf_paged=9</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sinna Lévé (ateliers et chantiers d'insertion)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sinnamary</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>sinna.leve973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0694 28 03 24</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.ville-sinnamary.fr/actualite/services-a-la-personne-de-lassociation-sinna-leve/</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Association Éclosion</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Cayenne</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>eclosion973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0694 15 84 11 (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://ville-cayenne.fr/wp-content/uploads/MAJ-16-04-RDV-AVRIL-2024.pdf</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ADER</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ader.kourou@orange.fr</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>06 94 44 40 67</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/ader/</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AKATIJ</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>f.poulain@akatij.fr</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>06 94 95 77 90</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/akatij/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ASSOCIATION PERFA973</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>guillaume.perfa973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>07 81 31 66 97</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/association-perfa973/</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>LA LOUPIOTE</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>laloupiote973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>06 94 40 13 19</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/la-loupiote/</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>MACAO GUYANE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>guyanemacao@gmail.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>06 94 91 04 35 06 94 01 93 81</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/macao-guyane/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TOE LOBIE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Macouria</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>toelobie@laposte.net</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>06 94 46 88 37</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.macouria.fr/annuaire/toe-lobie/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>ASSOCIATION DES LOCATAIRES DE MAYA</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Matoury</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>franck.falla@orange.fr</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>0694 26 85 08</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>https://www.ville-matoury.fr/nos-associations-culturelles</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>autre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G171"/>
+  <autoFilter ref="A1:G215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>nom_association</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>date_source</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>categorie</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>preuve_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Crèche Les Petits Papillons (structure associative : site associationlespetitspapillons.fr)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>crechelespetitspapillons@orange.fr</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0594 38 21 00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Crèche Raoul et Germaine (structure associative : site associationlespetitspapillons.fr)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>creche-raouletgermaine@orange.fr</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0594 35 22 09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Crèche Ti Moun (structure associative : site associationlespetitspapillons.fr)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>crechetimoun@orange.fr</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0594 30 54 93</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Crèche Pom'Kanel (association Bois Canon : site boiscanon973.fr, mail assoc-boiscanon.fr)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>directionpk@assoc-boiscanon.fr</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0594 31 72 45</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Crèche Pom'Damour (association Bois Canon : site boiscanon973.fr, mail assoc-boiscanon.fr)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>directionpa@assoc-boiscanon.fr</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0594 31 26 73</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Crèche Pom'Rosa (association Bois Canon : site boiscanon973.fr, mail assoc-boiscanon.fr)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Matoury</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>direction@assoc-boiscanon.fr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0594 39 37 13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.ville-matoury.fr/nos-creches</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>solidarité</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Commentaire HTML Webflow de la page « Last Published: Thu Oct 01 2026 16:19:40 GMT » + site actif (actualités et événements 2026 sur la page d'accueil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Association Kwata</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>asso@kwata.net</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/crb_event/nature-o-top-relevez-le-challenge-archeologique/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Date d'événement affichée sur la page mairie (13/06/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Touka Danses CDCN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>toukadanses.cdcnguyane@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>06 94 38 11 11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2025/11/BAT7-DEPLIANT-3V-2025.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Dépliant Rencontres de danses (PDF mairie), date de mise en ligne WP 2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tournoi de basket-ball 3x3 (contact Emile ROBINSON ; structure non nommée)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>doko.compagny973@gmail.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0694 97 27 61 / 0694 98 29 08 / 0594 21 39 20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Programme fête communale 8-10 septembre 2023 ; Programme officiel de la fête communale 8-10 septembre 2023 (PDF mairie), date de mise en ligne WP 2023-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tournoi de domino kontre (contact Jean-Marc BADETTE ; structure non nommée)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rémire-Montjoly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>badiobm@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0694 02 61 41</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://remire-montjoly.fr/wp-content/uploads/2023/09/PROGRAMME-FDRM-2023.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Programme fête communale 8-10 septembre 2023 ; Programme officiel de la fête communale 8-10 septembre 2023 (PDF mairie), date de mise en ligne WP 2023-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Union des Commerçants de l'Ile de Cayenne (UCIC)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cayenne</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>info.ucicayenne@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0694 92 84 04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Programme officiel des vacances juillet-août 2024 (PDF mairie), date de mise en ligne WP 2024-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ligue de roller et de skateboard Guyane</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cayenne</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>roller.extrascolaire@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>06 75 78 20 53</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://ville-cayenne.fr/wp-content/uploads/PROG-VAC-PV-2024.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Programme officiel des vacances juillet-août 2024 (PDF mairie), date de mise en ligne WP 2024-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pranavayu (organisatrice du 1er Salon Art, Bien-être &amp; Co ; nom exact non précisé dans la source)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kourou</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>asso.pranavayu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0694 16 97 27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.ville-kourou.fr/wp-content/uploads/2025/05/AGENDA-MAI-2025-dernier-1.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PDF agenda culturel de la mairie intitulé 'Mai 2025' (Service des Affaires Culturelles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Collectif des Renards Volants / CARMA (forme juridique non précisée)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>chercheursdart4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>06 94 31 13 52</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://mairie-mana.fr/crb_agenda/atelier-theatre-texte-jeu-carma/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>loisirs/culture</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>JSON-LD datePublished de la page (datePublished 2022-11-10) ; atelier du 11 novembre 2022</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6814,7 +9069,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Annuaires des clubs sportifs et des associations culturelles (pages non datées; site actif, actu du 23.9.2026). Exclus: amicale pompiers, église, Aquazonia (email municipal), Comité régional Sports pour Tous, Santé Pour Tous (seniors). Entrées sans email non retenues.</t>
+          <t>Complément solidarité : 45 pages du site (CCAS, MISE, DSU, contrat de ville, CLS, CLSPD, participation citoyenne, annuaires, 24 actualités/événements, PDF contrat de ville 2023, etc.) scannées. Seules associations de solidarité/social avec email : 6 crèches associatives (/nos-creches), statut associatif déduit des domaines associationlespetitspapillons.fr et assoc-boiscanon.fr / boiscanon973.fr. Exclus : Les Petits Sourires (statut non établi), emails @mairie-matoury.fr (services municipaux), concertation NPNRU, assomyob (déjà en base). Ile aux Enfants et Adi et Nana : pas d'email propre.</t>
         </is>
       </c>
     </row>
@@ -6836,7 +9091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Annuaire communal (8 pages) daté 2023-12-04 par métadonnées; exclus: Lions Club, Croix-Rouge, assistantes maternelles; DAAC Guyane et GPS écartés (nature associative incertaine). Taxonomie du site peu fiable (clubs étiquetés 'Assistantes Maternelles').</t>
+          <t>Complément : 80 fiches annuaire, 8 pages paginées /annuaire/paged-2/N/, 674 pages (agenda 272, actualités 307, pages 87, activités 8) et 213 PDF 2023-2026 scannés. Fiches annuaire sans contact hors liste paginée (ASAM, Chemin Demba, Mo Faya, Dynamo de Soula, ADER Guyane, Colombes, Be Active : aucun email). Nouveaux : DAAC Guyane, Drépaguyane, 2e email Athlétisme club de Soula. Écartés : GPS (p.monjo@gps.gf, nature inconnue), Lions Club et Croix-Rouge (exclus), Karting/Royal Ranch (entreprises commerciales), lespetitesgraines.guyane@gmail.com (organisateur Snoezelen 03/12/2025, nom d'association non établi), lafetwara@gmail.com (inscriptions Lafèt Wara, organisateur non précisé), asso.perfa1@gmail.com (Erasmus+ 2025, lien avec PERFA973 déduit seulement), cyrielle@kwata.net (crédit pied de page).</t>
         </is>
       </c>
     </row>
@@ -6848,7 +9103,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>irrécupérable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6858,7 +9113,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Site actif (actus oct. 2026) mais la page /service/associations/ ne contient aucun annuaire, aucune association ni PDF; seul email = contact@ville-cayenne.fr (mairie).</t>
+          <t>Site actif (actualités oct. 2026). Page associations vide, mais contacts d'associations lus dans les PDF d'agenda/programme vacances publiés par la mairie (wp-json media + pdftotext). Pas de guide/annuaire des associations publié ; PDF 'ventilation' des subventions sans emails.</t>
         </is>
       </c>
     </row>
@@ -6870,7 +9125,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>irrécupérable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6880,7 +9135,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Page /annuaire-des-associations/ vide ('recensera prochainement'); page vie associative sans association ni PDF; seul email = cabinet@remiremontjoly.fr (mairie).</t>
+          <t>Site actif (oct. 2026). Annuaire des associations toujours vide, mais coordonnées d'associations lues dans les pages d'événements/actualités 2021-2026 (sitemap crb_event/post) et dans le PDF programme de la fête communale 2023. Emails de mairie/agents municipaux exclus.</t>
         </is>
       </c>
     </row>
@@ -6897,12 +9152,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.montsinery-tonnegrande.fr</t>
+          <t>https://www.montsinery-tonnegrande.fr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Site non actif (dernière actualité 14/04/2022, contenus 2016-2017); pas d'annuaire d'associations ni PDF; seul email = mairie.</t>
+          <t>Dernier contenu avril 2022 (site inactif). Posts/pages/PDF 2021-2022 (REST API WordPress) ne contiennent aucun contact d'association ; emails associations/commerces trouvés tous datés 2016-2018. Pas de sitemap.</t>
         </is>
       </c>
     </row>
@@ -6919,12 +9174,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>roura.gf</t>
+          <t>https://roura.gf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Site inaccessible: HTTP 503 (WebFetch) et certificat TLS auto-signé (curl); aucune donnée récupérable.</t>
+          <t>Seul site officiel roura.gf : certificat TLS auto-signé (curl erreur 60), non contourné conformément à la consigne ; aucun autre domaine officiel joignable (roura.fr, mairie-roura.fr, etc. : échec de connexion).</t>
         </is>
       </c>
     </row>
@@ -6941,12 +9196,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>http://www.grandsanti.fr</t>
+          <t>https://grandsanti.fr</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Site officiel actif (actualités oct. 2026). Page /l-assoc liste 4 associations (TAPOE I PANGI, Wi Na Wi, Lawa étoiles, A.F.P. Association Fiiman Pikin / Fiiman Sten) mais sans aucun email ni téléphone ; /sport-et-loisirs ne liste que des terrains ; /annuaire-local ne contient que mairie, dispensaire, gendarmerie, commerces et transporteurs (aucune association). Aucun PDF vie associative. Seuls emails trouvés = mairie/commerces, hors périmètre.</t>
+          <t>Site actif (actus 11-14 oct. 2026). Re-lecture du HTML brut de /l-assoc : 5 associations (TAPOE I PANGI, Wi Na Wi, Lawa étoiles, A.F.P., Fiiman Sten) avec champs « membres/secteur » vides, aucun email ni téléphone ; /annuaire-local (mairie@, dispensaire, commerces) et /sport-et-loisirs (terrains) sans association ; aucun PDF ni actualité avec contact d'association.</t>
         </is>
       </c>
     </row>
@@ -6968,7 +9223,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Site officiel WordPress actif (actualités sept. 2026). Aucune page vie associative / annuaire des associations (sitemap, pages et 23 articles vérifiés), aucun PDF ; seul email = contact@papaichton.fr (mairie, mentions légales).</t>
+          <t>Site actif (WordPress, 2026). REST : 38 pages/articles + 8 PDF 2026 scannés : aucune rubrique associative. Seuls emails = mairie@/contact@papaichton.fr, écoles, et PDF communiqué Parc amazonien (Jeux Aluku, mai 2026) citant des personnes (freddie.dikan@hotmail.com, agents du Parc) = contacts individuels, non associatifs, exclus.</t>
         </is>
       </c>
     </row>
@@ -6986,7 +9241,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aucun site officiel de mairie fonctionnel trouvé : ville-maripasoula.fr (domaine parqué chez Gandi), maripasoula.gf (parking Oxyd), autres domaines candidats inexistants ; l'annuaire service-public ne renseigne pas de site. Pas de page ni PDF associatif de mairie accessible.</t>
+          <t>ville-maripasoula.fr : domaine parqué (Gandi), connexion réinitialisée ; maripasoula.gf : erreur certificat TLS (non contournée). Aucun site officiel indexé (annuaires tiers : « non disponible »).</t>
         </is>
       </c>
     </row>
@@ -7004,7 +9259,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pas de site officiel de mairie (mention « site internet : à venir » ; mairie joignable seulement par mairie.saul@orange.fr, hors périmètre associations). Aucune page vie associative ni PDF de mairie.</t>
+          <t>Aucun site officiel (annuaires : « site non disponible » ; mairie.saul@orange.fr = mairie) ; domaines candidats saul.fr/.gf, mairie-/ville-/commune-saul.fr inexistants.</t>
         </is>
       </c>
     </row>
@@ -7016,7 +9271,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>irrécupérable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7026,7 +9281,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Site actif (actualités 2026) mais aucune source associative datée 2021-2026 contenant des emails. Page 'Sports proposés par des associations' (56 clubs, emails présents) : dateModified 2017-06-05 (antérieure à 2021, exclue). Annuaire des associations = PDF 'Contrat de Ville 2020' (mise à jour 16/10/2020, exclu) et flipbook Calaméo (hébergé sur site tiers, publié 2015-08-13, exclu). Seul email trouvé = vie.asso@ville-kourou.fr (service municipal, pas une association).</t>
+          <t>Site actif (actualités jusqu'en oct. 2026). Pas de guide/annuaire d'associations récent avec emails : annuaire PDF 2020, page sports 2017 (exclus) ; Journée des associations 2025/2026, appels à projets 2026 et formation gestion associative sans emails d'associations (seul vieassociativekourou@gmail.com = service municipal, exclu). 11 contacts extraits d'actualités/agenda datés 2021-2026 et de PDF d'agenda culturel 2025. Exclus : CCDS, Ligue de l'enseignement, MGO/Miss Guyane, artiste individuel, emails d'exposants.</t>
         </is>
       </c>
     </row>
@@ -7038,7 +9293,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>irrécupérable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7048,7 +9303,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Annuaire officiel des associations (https://www.ville-sinnamary.fr/categorie-annuaire/associations/, 38 entrées, site actif © 2026) mais uniquement noms, téléphones et adresses : aucun email publié sur la page, ni sur les pages sports/subventions. Aucun contact avec email exploitable ; entrées téléphone seul non retenues.</t>
+          <t>Annuaire (38 assos) et fiches sans emails ; sitemap complet analysé (481 pages, emails encodés en entités HTML décodés). 3 emails d'associations trouvés dans des actualités datées 2023-2024 (date via API REST WordPress car pas de JSON-LD). Exclus : PNRG, SEPANGUY, MFR, employeurs, adresses ville-sinnamary.fr.</t>
         </is>
       </c>
     </row>
@@ -7063,10 +9318,14 @@
           <t>irrécupérable</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://iracoubo.fr/</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aucun site officiel de mairie accessible/indexé (iracoubo.fr : DNS/proxy en échec ; la mairie n'apparaît que sur Facebook et service-public). Pas de page vie associative trouvée.</t>
+          <t>Réessai : https et http, avec et sans www, sitemap.xml, variantes (mairie-/ville-/commune-iracoubo.fr, iracoubo.com) ; échec : tunnel proxy 502 en https et 'Could not resolve host' en http (DNS) ; Tavily map refuse l'URL (400). Aucun site officiel joignable ; recherche web ne renvoie que des sources tierces/exclues (annuaires, service-public, Facebook).</t>
         </is>
       </c>
     </row>
@@ -7084,7 +9343,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pas de site officiel de mairie trouvé (uniquement page Facebook, annuaire service-public et annuaires tiers). Pas de page associative.</t>
+          <t>saint-elie.gf résout mais connexion réinitialisée (curl 35 ; Tavily échec) ; aucun site officiel indexé (annuaires tiers : « site non disponible » ; mairie.stelie@orange.fr = mairie).</t>
         </is>
       </c>
     </row>
@@ -7099,14 +9358,10 @@
           <t>irrécupérable</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>mairie-regina.fr (domaine d'email seulement)</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aucun site web de mairie accessible : mairie-regina.fr injoignable (échec tunnel/DNS), non indexé par les moteurs. Pas de page associative accessible.</t>
+          <t>mairie-regina.fr résout en DNS (OVH) mais connexion HTTPS réinitialisée (curl 35) et Tavily 'Failed to fetch' ; www.regina.fr = autre site (404). Recherches web : aucun site officiel indexé, annuaires tiers indiquent « site non disponible ».</t>
         </is>
       </c>
     </row>
@@ -7121,14 +9376,10 @@
           <t>irrécupérable</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>villesaintgeorgesdeloyapock.fr (domaine d'email seulement)</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aucun site web de mairie résolvable (DNS en échec sur villesaintgeorgesdeloyapock.fr) ; seule présence : Instagram et service-public (sources exclues). Pas de page associative.</t>
+          <t>villesaintgeorgesdeloyapock.fr (domaine des emails de la mairie) : DNS inexistant (aussi avec www, Tavily échec). saint-georges.fr = portail générique dataxy multi-communes non officiel (exclu). Variantes .gf/mairie-* inexistantes. Aucun site officiel trouvé.</t>
         </is>
       </c>
     </row>
@@ -7146,7 +9397,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pas de site officiel de mairie trouvé ; uniquement annuaires tiers/service-public. Pas de page associative.</t>
+          <t>Aucun site officiel : recherches web (annuaires tiers/Banatic seulement, mairie.annexeouanary@orange.fr = mairie), domaines candidats ouanary.fr/.gf, mairie-/ville-/commune-ouanary.fr inexistants.</t>
         </is>
       </c>
     </row>
@@ -7163,12 +9414,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://ville-camopi.fr/</t>
+          <t>https://ville-camopi.fr</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Site actif (WordPress, mises à jour sept. 2026) mais sans page vie associative/annuaire des associations : sitemap = pages, élus, services, établissements (collège, hall sportif, gendarmerie, poste, etc.), événements. Aucun email d'association.</t>
+          <t>Site actif (sitemaps lastmod sept. 2026). 59 URLs (articles, pages, événements, établissements, services) + REST scannés : aucune page associative ni PDF ; seuls emails = contact@ville-camopi.fr (mairie), aérodrome, centre de santé, collège.</t>
         </is>
       </c>
     </row>
@@ -7202,17 +9453,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>irrécupérable</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://mairie-mana.fr</t>
+          <t>https://mairie-mana.fr/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Site actif (actualités juin 2026) mais l'annuaire des associations (rubrique 'Associations culturelles et sportives', 61 fiches crb_annuaire) n'expose aucun email ni téléphone d'association (fiches vides, seulement l'email générique de la mairie); dernières fiches modifiées 2022 sans coordonnées.</t>
+          <t>Site actif (agenda jusqu'en juin 2026). 61 fiches d'annuaire sans emails d'associations ; sitemap complet analysé (2555 pages dont ~1440 événements d'agenda). 9 contacts extraits d'événements d'agenda datés 2021-2025. PDF subvention/agenda événementiel sans emails d'associations. Exclus : OTOG, GEPOG, PNRG, comité régional de cyclisme (fédération), amicale pompiers, MFR, CCAS, chambres consulaires, centre social Makandra (municipal).</t>
         </is>
       </c>
     </row>
@@ -7229,12 +9480,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.awala-yalimapo.fr</t>
+          <t>awala-yalimapo.fr</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Site inaccessible: HTTPS en erreur (aucun certificat SSL, HTTP 503), la version http redirige via frameset vers awala-yalimapo.mairies-guyane.org qui ne résout pas (DNS). Aucune page associative ni date.</t>
+          <t>Retentative : https://awala-yalimapo.fr et www. = erreur certificat TLS (curl 60, non contournée). awala-yalimapo.mairies-guyane.org : DNS inexistant ; mairies-guyane.org est un site SEO/casino non officiel (exclu). Variantes mairie-/ville-awala-yalimapo.fr/.com/.gf : inexistantes. La version http n'a servi qu'à lire l'en-tête : page statique last-modified 2012-05-16 (hors fenêtre 2021-2026). Recherche web : aucun site officiel alternatif.</t>
         </is>
       </c>
     </row>
@@ -7256,7 +9507,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Site actif (actualités août 2026) mais seule rubrique 'Vie associative' = fiche Régie des territoires (Kumaku) sans email ni téléphone; pas d'annuaire; email secretariat@ville-apatou.fr = mairie, non associatif.</t>
+          <t>Site actif (actus août 2026). Scan complet REST (88 pages/articles) + 36 PDF (délibérations 2023-2026, avis EDF) : « Maison des associations » = « contenu à venir », fiche Régie des territoires Kumaku sans email, MFR (mfr.apatou@mfr.asso.fr, 2023) = réseau national MFR exclu, communicationapatou@gmail.com (communiqué Caravane du Tennis 2024, adresse communication d'Apatou/probablement municipale) exclu, emails @ville-apatou.fr = agents. Association Sabi Wie Lutu citée sans contact.</t>
         </is>
       </c>
     </row>
